--- a/Phân Công Nhóm 5 update.xlsx
+++ b/Phân Công Nhóm 5 update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\LTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C1CBA7-C4B2-43FB-8B42-0C2D63384102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774D3EE4-CF8F-40C3-BB4C-CD41B9643AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,8 +600,12 @@
       <c r="C6" s="2">
         <v>0</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
       <c r="F6" s="2">
         <v>0.5</v>
       </c>
